--- a/src/CADA/result_from_disease.xlsx
+++ b/src/CADA/result_from_disease.xlsx
@@ -358,30 +358,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>patient_id</t>
+          <t>Case_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>features</t>
+          <t>HPO_terms</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>results</t>
+          <t>Gene</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>CADA_top30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>CADA_rank</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Patient:0</t>
+          <t>Patient:482816</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -391,14 +401,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DYRK1A,QARS1,CIT,HCFC1,RNF168,YME1L1,POMT2,WDR62,PGAP2,FH</t>
-        </is>
+          <t>FKRP</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DYRK1A,QARS1,CIT,HCFC1,RNF168,YME1L1,POMT2,WDR62,PGAP2,FH,UQCC2,ZNHIT3,ZNF711,ADK,PARS2,DHPS,TUBB2B,EMC1,AP3D1,KIF2A,ALG11,DOCK7,PDHA1,OCLN,NDE1,CDK5,AP4S1,SARS1,EEF1A2,KATNB1</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Patient:1</t>
+          <t>Patient:482812</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -408,14 +426,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FLNA,PEX3,MARS2,ALG9,FTO,CEP290,PIGY,BCL11B,ATP7A,ZBTB24</t>
-        </is>
+          <t>SHOC2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FLNA,PEX3,MARS2,ALG9,FTO,CEP290,PIGY,BCL11B,ATP7A,ZBTB24,ERCC2,KPTN,LGI4,ATP6V1A,POU1F1,PIEZO2,COL3A1,DDX11,SC5D,TBCE,ATIC,PRKDC,CRLF1,PEX2,STAC3,FGFR3,KDM5C,ZBTB20,LTBP4,CENPJ</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>479</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Patient:2</t>
+          <t>Patient:482807</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -425,14 +451,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TUBB3,TMEM216,CSPP1,B3GALNT2,PAK1,SLC9A6,ACADS,GABBR2,CPT2,SLC35A3</t>
-        </is>
+          <t>CTC1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TUBB3,TMEM216,CSPP1,B3GALNT2,PAK1,SLC9A6,ACADS,GABBR2,CPT2,SLC35A3,NUP107,NAGLU,CCDC174,GLUL,DMXL2,CPLANE1,DPAGT1,DNA2,L1CAM,ARNT2,WDR26,COL13A1,ZDHHC9,FARSB,COG6,KIF14,GNS,CNKSR2,TRMT10A,SLC17A5</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>867</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Patient:3</t>
+          <t>Patient:482806</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -442,14 +476,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TUBB3,TMEM216,CSPP1,B3GALNT2,PAK1,SLC9A6,ACADS,GABBR2,CPT2,SLC35A3</t>
-        </is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TUBB3,TMEM216,CSPP1,B3GALNT2,PAK1,SLC9A6,ACADS,GABBR2,CPT2,SLC35A3,NUP107,NAGLU,CCDC174,GLUL,DMXL2,CPLANE1,DPAGT1,DNA2,L1CAM,ARNT2,WDR26,COL13A1,ZDHHC9,FARSB,COG6,KIF14,GNS,CNKSR2,TRMT10A,SLC17A5</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2452</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Patient:4</t>
+          <t>Patient:482804</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -459,14 +501,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PALB2,FANCL,IDUA,POLR1D,TTC37,BRCA1,ADAMTS18,RBBP8,PAX1,FANCA</t>
-        </is>
+          <t>EVC2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PALB2,FANCL,IDUA,POLR1D,TTC37,BRCA1,ADAMTS18,RBBP8,PAX1,FANCA,FKBP14,CLCF1,KREMEN1,NBN,MITF,TSHB,CDKN1C,H19,KCNQ1OT1,KCNQ1,H19-ICR,IGF2,TBX15,HRAS,NRAS,INTU,CREB3L1,GALNS,FREM1,DNAJC21</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>233</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Patient:5</t>
+          <t>Patient:482800</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -476,14 +526,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DST,TMEM67,MYL1,TUBB6,CHRNB1,ERCC3,LARS2,ALG6,TREX1,NDP</t>
-        </is>
+          <t>AMPD1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DST,TMEM67,MYL1,TUBB6,CHRNB1,ERCC3,LARS2,ALG6,TREX1,NDP,ECHS1,GPHN,GLRA1,MYBPC1,PEX5,GFAP,SLC18A2,WFS1,ANTXR2,SLC5A7,TNFRSF11B,LAMB2,PCBD1,AP1S1,SELENON,TCIRG1,BBS10,GAA,COL18A1,SYNE1</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>475</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Patient:6</t>
+          <t>Patient:482797</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -493,14 +551,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HNRNPH2,KIAA1109,RAC1,CLP1,ATRX,SHROOM4,CASK,WDR4,EBF3,SLC45A1</t>
-        </is>
+          <t>MAP2K2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HNRNPH2,KIAA1109,RAC1,CLP1,ATRX,SHROOM4,CASK,WDR4,EBF3,SLC45A1,FUT8,HS6ST2,TLK2,STAMBP,PIGT,USP9X,KIF11,KMT2E,TCF20,ARCN1,DOCK6,CDK10,RBMX,STRADA,KAT6A,COG7,DCPS,HECW2,TMEM237,MBD5</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>483</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Patient:7</t>
+          <t>Patient:482792</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -510,14 +576,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MTO1,MECP2,MAST1,AGTPBP1,VPS53,NEUROD2,WWOX,WDR81,EARS2,CACNA1E</t>
-        </is>
+          <t>NKX2-1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MTO1,MECP2,MAST1,AGTPBP1,VPS53,NEUROD2,WWOX,WDR81,EARS2,CACNA1E,SLC25A12,POMT2,GNAO1,EXOSC9,GUF1,LAMB1,TSEN2,SERAC1,COPB2,SPTAN1,MPDU1,ISCA1,COQ9,MPC1,SLC25A1,PNPO,ACOX1,NTRK2,SUFU,HSPD1</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>765</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Patient:8</t>
+          <t>Patient:482779</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -527,14 +601,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CCDC47,DDX11,BRPF1,NONO,PRKDC,PEX1,ALG9,AGA,ARX,EBP</t>
-        </is>
+          <t>GHR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CCDC47,DDX11,BRPF1,NONO,PRKDC,PEX1,ALG9,AGA,ARX,EBP,ZNF148,ERCC6,PIGO,PEX3,SMARCC2,KDM5B,MED25,POLR3A,HERC1,PIGY,PGAP3,MARS2,PSAT1,PPP2CA,FLVCR2,PPP1R15B,TBCE,GNB5,STAC3,MKRN3</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1209</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Patient:9</t>
+          <t>Patient:482774</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -544,14 +626,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SHROOM4,CLP1,ARX,LAS1L,ZC4H2,TLK2,CASK,EBF3,FUT8,TMEM237</t>
-        </is>
+          <t>BTD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SHROOM4,CLP1,ARX,LAS1L,ZC4H2,TLK2,CASK,EBF3,FUT8,TMEM237,PPM1D,COG7,RAC1,SLC45A1,KIF11,PIGN,BCL11B,DCPS,KIAA1109,ATRX,GATAD2B,PIGT,HNRNPH2,SOX4,STAMBP,FOXP1,KAT6A,USP9X,TAF1,PPP1R15B</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2480</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Patient:10</t>
+          <t>Patient:482772</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -561,14 +651,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SHROOM4,CLP1,ARX,LAS1L,ZC4H2,TLK2,CASK,EBF3,FUT8,TMEM237</t>
-        </is>
+          <t>WNT10A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SHROOM4,CLP1,ARX,LAS1L,ZC4H2,TLK2,CASK,EBF3,FUT8,TMEM237,PPM1D,COG7,RAC1,SLC45A1,KIF11,PIGN,BCL11B,DCPS,KIAA1109,ATRX,GATAD2B,PIGT,HNRNPH2,SOX4,STAMBP,FOXP1,KAT6A,USP9X,TAF1,PPP1R15B</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2488</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Patient:11</t>
+          <t>Patient:482762</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -578,14 +676,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SHROOM4,CLP1,ARX,LAS1L,ZC4H2,TLK2,CASK,EBF3,FUT8,TMEM237</t>
-        </is>
+          <t>COL4A3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SHROOM4,CLP1,ARX,LAS1L,ZC4H2,TLK2,CASK,EBF3,FUT8,TMEM237,PPM1D,COG7,RAC1,SLC45A1,KIF11,PIGN,BCL11B,DCPS,KIAA1109,ATRX,GATAD2B,PIGT,HNRNPH2,SOX4,STAMBP,FOXP1,KAT6A,USP9X,TAF1,PPP1R15B</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2632</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Patient:12</t>
+          <t>Patient:482704</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -595,14 +701,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KMT2D,KDM6A,CDC6,POC1A,DSE,KAT6B,PEX5,PIK3CA,KAT6B,POLE</t>
-        </is>
+          <t>MYH3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>KMT2D,KDM6A,CDC6,POC1A,DSE,KAT6B,PEX5,PIK3CA,KAT6B,POLE,ATP6V0A2,KMT2A,CEP57,UBE2A,FIBP,KIAA0586,TRAIP,PIEZO2,PYCR1,PIGL,TCTN2,FBXL3,TGDS,NAA10,GPC4,ANKRD11,RSPRY1,FBN2,MGAT2,CAMK2G</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>276</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Patient:13</t>
+          <t>Patient:482694</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -612,14 +726,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SLC6A9,TCF4,ASPM,RAB3GAP2,POMT2,POMT1,FKTN,FKRP,LARGE1,KCNJ6</t>
-        </is>
+          <t>GLI2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SLC6A9,TCF4,ASPM,RAB3GAP2,POMT2,POMT1,FKTN,FKRP,LARGE1,KCNJ6,EEF1A2,CENPE,PSAT1,AGA,DHPS,ERCC1,CDK5,NSDHL,PEX26,KLHL15,FLVCR2,MEF2C,TTI2,EMC1,UQCC2,PGAP2,ERCC6,HOXB1,ZNF335,BCORL1</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>491</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Patient:14</t>
+          <t>Patient:482678</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -629,14 +751,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SLC6A9,TCF4,ASPM,RAB3GAP2,POMT2,POMT1,FKTN,FKRP,LARGE1,KCNJ6</t>
-        </is>
+          <t>PIGL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SLC6A9,TCF4,ASPM,RAB3GAP2,POMT2,POMT1,FKTN,FKRP,LARGE1,KCNJ6,EEF1A2,CENPE,PSAT1,AGA,DHPS,ERCC1,CDK5,NSDHL,PEX26,KLHL15,FLVCR2,MEF2C,TTI2,EMC1,UQCC2,PGAP2,ERCC6,HOXB1,ZNF335,BCORL1</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>736</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Patient:15</t>
+          <t>Patient:482626</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -646,14 +776,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EIF2S3,AP4S1,TUBA1A,PDHX,IQSEC2,SARS1,P4HTM,RHOBTB2,MYMK,PARS2</t>
-        </is>
+          <t>PIGL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EIF2S3,AP4S1,TUBA1A,PDHX,IQSEC2,SARS1,P4HTM,RHOBTB2,MYMK,PARS2,RAB11B,TBCD,CCDC88C,FKTN,QARS1,CLCN4,ALG3,PLAA,AP4M1,UBE3A,YME1L1,CIT,NAT8L,MFSD2A,ADSL,B4GAT1,AP4E1,CNTNAP1,LAGE3,PHACTR1</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1498</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Patient:16</t>
+          <t>Patient:482627</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -663,14 +801,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EIF2S3,AP4S1,TUBA1A,PDHX,IQSEC2,SARS1,P4HTM,RHOBTB2,MYMK,PARS2</t>
-        </is>
+          <t>MECP2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EIF2S3,AP4S1,TUBA1A,PDHX,IQSEC2,SARS1,P4HTM,RHOBTB2,MYMK,PARS2,RAB11B,TBCD,CCDC88C,FKTN,QARS1,CLCN4,ALG3,PLAA,AP4M1,UBE3A,YME1L1,CIT,NAT8L,MFSD2A,ADSL,B4GAT1,AP4E1,CNTNAP1,LAGE3,PHACTR1</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Patient:17</t>
+          <t>Patient:482628</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -680,14 +826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TCTN3,GNAS,OTX2,LBR,FOXL2,POLD1,TINF2,IDUA,THRA,YY1AP1</t>
-        </is>
+          <t>ABCA4</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TCTN3,GNAS,OTX2,LBR,FOXL2,POLD1,TINF2,IDUA,THRA,YY1AP1,ERCC4,PAX6,CRYAA,PDE6D,SOST,SRD5A3,NOP10,NHP2,PTF1A,WNT1,CRIPT,RNF113A,MYH8,ALDOA,GLDN,DKC1,MBTPS2,PROKR2,PROK2,FAM111A</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2883</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Patient:18</t>
+          <t>Patient:482629</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -697,14 +851,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MTO1,MECP2,TSEN2,WWOX,SUFU,EXOSC9,ACOX1,ATAD1,AGTPBP1,NEUROD2</t>
-        </is>
+          <t>CTBP1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MTO1,MECP2,TSEN2,WWOX,SUFU,EXOSC9,ACOX1,ATAD1,AGTPBP1,NEUROD2,SLC25A12,POMT2,EARS2,SPTAN1,VPS53,MAST1,SIL1,ISCA1,WDR81,DYNC1H1,HTT,MPDU1,COQ9,MPC1,GUF1,KCNT2,CACNA1E,DPM1,CTSD,DDHD2</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>197</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Patient:19</t>
+          <t>Patient:482630</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -714,14 +876,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ZBTB20,PIEZO2,LONP1,PBX1,KCNH1,CACNA1C,FGFR3,ATIC,ATP6V1A,MYO18B</t>
-        </is>
+          <t>CASK</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ZBTB20,PIEZO2,LONP1,PBX1,KCNH1,CACNA1C,FGFR3,ATIC,ATP6V1A,MYO18B,KRAS,SOX2,SIX6,PUF60,PPP3CA,POU1F1,GLI2,PRKD1,GNE,SMS,MARS2,FTO,NFIB,CHD8,ATN1,BMP4,LGI4,KDM5C,ERCC2,MED12</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>729</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Patient:20</t>
+          <t>Patient:482608</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -731,14 +901,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PSAP,ARX,NDUFA9,NDUFS8,KCTD7,MTPAP,GJC2,NUP214,UBTF,NDUFS7</t>
-        </is>
+          <t>CHD8</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PSAP,ARX,NDUFA9,NDUFS8,KCTD7,MTPAP,GJC2,NUP214,UBTF,NDUFS7,MFF,AP5Z1,ATP6AP2,SQSTM1,PTS,CERS1,CWF19L1,UCHL1,VWA3B,FA2H,CTSF,PEX10,PIK3R5,NDUFB9,SDHA,SDHD,SDHAF1,NARS2,KIF1C,TTC19</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2724</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Patient:21</t>
+          <t>Patient:482611</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -748,14 +926,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IREB2,ADSL,BRAT1,DEAF1,ZBTB11,MFSD2A,TECPR2,UFC1,SLC1A2,RAB11B</t>
-        </is>
+          <t>SHANK3</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>IREB2,ADSL,BRAT1,DEAF1,ZBTB11,MFSD2A,TECPR2,UFC1,SLC1A2,RAB11B,FRA16E,DNM1L,SPATA5,LRPPRC,SARS1,RHOBTB2,AP4M1,LINS1,PLAA,NACC1,ITPA,PIGC,TRIT1,FOXG1,CLIC2,LIAS,DPM1,KCNT2,NECAP1,MTHFS</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>958</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Patient:22</t>
+          <t>Patient:482612</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -765,133 +951,193 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ZNF335,SLC35A2,NDE1,COASY,DOCK7,ALG11,KIF5C,POLA1,WDR26,HERC2</t>
-        </is>
+          <t>AHI1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ZNF335,SLC35A2,NDE1,COASY,DOCK7,ALG11,KIF5C,POLA1,WDR26,HERC2,WDR62,DHPS,PGAP2,UQCC2,POMT2,PEX26,RNF168,SLC6A9,ARNT2,METTL23,GNS,EMC1,AP3D1,ARFGEF2,ASCC1,CPLANE1,GPSM2,HCFC1,TCF4,OCLN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Patient:24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Gait ataxia,Oculomotor apraxia,Seizures,Horizontal nystagmus,Specific learning disability,Attention deficit hyperactivity disorder,Dysdiadochokinesis</t>
-        </is>
-      </c>
+          <t>Patient:482613</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NTRK2,KCNT1,EEF1A2,SLC17A5,MFSD8,CACNA1B,DNAJC12,WDR81,SLC25A1,GABRG2</t>
-        </is>
+          <t>GFAP</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ZNF335,SLC35A2,NDE1,COASY,DOCK7,ALG11,KIF5C,POLA1,WDR26,HERC2,WDR62,DHPS,PGAP2,UQCC2,POMT2,PEX26,RNF168,SLC6A9,ARNT2,METTL23,GNS,EMC1,AP3D1,ARFGEF2,ASCC1,CPLANE1,GPSM2,HCFC1,TCF4,OCLN</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Patient:25</t>
+          <t>Patient:482617</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Global developmental delay,Abnormal external genitalia,Abnormality of eye movement,Delayed speech and language development,Motor delay,Microcephaly,Muscular hypotonia</t>
+          <t>Gait ataxia,Oculomotor apraxia,Seizures,Horizontal nystagmus,Specific learning disability,Attention deficit hyperactivity disorder,Dysdiadochokinesis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>QARS1,LINS1,PARS2,CLIC2,KATNB1,SARS1,CIT,DYRK1A,ITPA,AP4S1</t>
-        </is>
+          <t>DNA2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NTRK2,KCNT1,EEF1A2,SLC17A5,MFSD8,CACNA1B,DNAJC12,WDR81,SLC25A1,GABRG2,GRIN2B,MAST1,TSEN54,TAF2,AGTPBP1,HPRT1,COPB2,LAMB1,PNPT1,LMNB2,MPC1,COQ9,CACNA1E,PCDH19,EARS2,SUCLG1,ALDH18A1,CUX2,GRIN2B,QDPR</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>890</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Patient:26</t>
+          <t>Patient:482618</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Early onset absence seizures,Infantile spasms</t>
+          <t>Global developmental delay,Abnormal external genitalia,Abnormality of eye movement,Delayed speech and language development,Motor delay,Microcephaly,Muscular hypotonia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FOXE3,KCNJ13,CPAMD8,ALPK3,CA2,PNPLA6,OCA2,MC1R,GNRH1,PKD1</t>
-        </is>
+          <t>MECP2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>QARS1,LINS1,PARS2,CLIC2,KATNB1,SARS1,CIT,DYRK1A,ITPA,AP4S1,ADK,ZNHIT3,ADSL,HCFC1,ELP2,AP4E1,LIAS,FH,LMAN2L,RAB11B,EIF2S3,ZBTB11,ARF1,TECPR2,MFSD2A,MRPS22,AP4M1,PIGP,IER3IP1,CCDC88C</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>141</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Patient:27</t>
+          <t>Patient:482619</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Astigmatism,Bifid uvula,Hypermetropia,Global developmental delay,Hyperopic astigmatism,Short stature,Broad neck,Wide nose,Abnormal facial shape,Epicanthus,Hypoplastic philtrum,Long philtrum,Midface retrusion,Snoring,Single transverse palmar crease,Sleep apnea,Anteverted nares</t>
+          <t>Early onset absence seizures,Infantile spasms</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DPF2,BMP1,BRAF,AMMECR1,SC5D,BMP4,C2CD3,FIBP,MGAT2,ALX4</t>
-        </is>
+          <t>FTCD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FOXE3,KCNJ13,CPAMD8,ALPK3,CA2,PNPLA6,OCA2,MC1R,GNRH1,PKD1,TNFRSF11A,MCM8,STAT3,NDP,SLC16A1,TRIM32,PAX2,ST14,NKX2-5,HNF4A,ELMO2,TUBB3,GATA3,ROBO3,HSD11B1,HMX1,NPHS1,SLC29A3,PLVAP,TGM1</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>196</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Patient:28</t>
+          <t>Patient:482620</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Respiratory failure,Bradycardia,Infantile muscular hypotonia,Abnormal eyelid morphology,Narrow forehead,Abnormal facial shape,Long fingers,Long toe,Low-set ears,Polyhydramnios,Posteriorly rotated ears,Prominent forehead</t>
+          <t>Astigmatism,Bifid uvula,Hypermetropia,Global developmental delay,Hyperopic astigmatism,Short stature,Broad neck,Wide nose,Abnormal facial shape,Epicanthus,Hypoplastic philtrum,Long philtrum,Midface retrusion,Snoring,Single transverse palmar crease,Sleep apnea,Anteverted nares</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PEX5,LTBP4,DHCR24,NEK9,ATP6V1B2,CRLF1,PYCR1,MYO18B,ATP6V1A,COL3A1</t>
-        </is>
+          <t>PPM1D</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DPF2,BMP1,BRAF,AMMECR1,SC5D,BMP4,C2CD3,FIBP,MGAT2,ALX4,FRMD4A,CTU2,POC1A,FAT4,SMARCA2,CEP57,ANKRD11,UBE2A,KMT2D,KDM6A,ATP6V0A2,EED,PYCR1,KAT6B,CSNK2A1,ALG12,LGI4,HNRNPK,FANCI,FBN2</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>371</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Patient:29</t>
+          <t>Patient:482621</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Abnormal renal morphology,Abnormality of limb bone morphology</t>
+          <t>Respiratory failure,Bradycardia,Infantile muscular hypotonia,Abnormal eyelid morphology,Narrow forehead,Abnormal facial shape,Long fingers,Long toe,Low-set ears,Polyhydramnios,Posteriorly rotated ears,Prominent forehead</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LMBR1,RAD21,GLI3,DSC3,BHLHA9,PRG4,CLCN5,NKX3-2,TP63,FBLN1</t>
-        </is>
+          <t>MTM1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PEX5,LTBP4,DHCR24,NEK9,ATP6V1B2,CRLF1,PYCR1,MYO18B,ATP6V1A,COL3A1,MGAT2,POLE,CEP55,PIEZO2,FIBP,ATR,ALKBH8,POU1F1,NFIB,RPS23,PBX1,FTO,LGI4,KRAS,FGFR3,TENM3,POC1A,FLNA,B9D2,LONP1</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1281</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Patient:30</t>
+          <t>Patient:482623</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Autistic behavior,Intellectual disability,Seizures,Polycystic kidney dysplasia,Abnormal social behavior,Angiofibromas,Infantile spasms,Repetitive compulsive behavior,Abnormal social behavior,Delayed speech and language development,Polycystic kidney dysplasia</t>
+          <t>Abnormal renal morphology,Abnormality of limb bone morphology</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SETD2,TKT,CBS,CRADD,GK,KCNH1,INPP5E,SOBP,GTF2E2,NAGLU</t>
-        </is>
+          <t>RPGRIP1L</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LMBR1,RAD21,GLI3,DSC3,BHLHA9,PRG4,CLCN5,NKX3-2,TP63,FBLN1,SMAD6,AXIN1,PHEX,COL9A1,HBB,HBG1,HBG2,BMPR1B,GDF5,BMP2,LRP5,BMPR1B,COL10A1,EDA,MATN3,ZNF141,IL10RB,SRY,NKX2-5,GDF5</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1140</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Patient:31</t>
+          <t>Patient:482552</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -901,14 +1147,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SETD2,TKT,CBS,CRADD,GK,KCNH1,INPP5E,SOBP,GTF2E2,NAGLU</t>
-        </is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SETD2,TKT,CBS,CRADD,GK,KCNH1,INPP5E,SOBP,GTF2E2,NAGLU,SLC35A3,SRD5A3,ZDHHC9,PAK1,MAB21L1,HESX1,GPR88,MBTPS2,IFT172,ARNT2,ARX,IDS,PEX14,GPSM2,CPT2,RBM12,RNPC3,KIF7,PTF1A,SNIP1</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3463</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Patient:32</t>
+          <t>Patient:482558</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -918,14 +1172,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SETD2,TKT,CBS,CRADD,GK,KCNH1,INPP5E,SOBP,GTF2E2,NAGLU</t>
-        </is>
+          <t>BTD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SETD2,TKT,CBS,CRADD,GK,KCNH1,INPP5E,SOBP,GTF2E2,NAGLU,SLC35A3,SRD5A3,ZDHHC9,PAK1,MAB21L1,HESX1,GPR88,MBTPS2,IFT172,ARNT2,ARX,IDS,PEX14,GPSM2,CPT2,RBM12,RNPC3,KIF7,PTF1A,SNIP1</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2326</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Patient:33</t>
+          <t>Patient:482568</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -935,14 +1197,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SETD2,TKT,CBS,CRADD,GK,KCNH1,INPP5E,SOBP,GTF2E2,NAGLU</t>
-        </is>
+          <t>HEXB</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SETD2,TKT,CBS,CRADD,GK,KCNH1,INPP5E,SOBP,GTF2E2,NAGLU,SLC35A3,SRD5A3,ZDHHC9,PAK1,MAB21L1,HESX1,GPR88,MBTPS2,IFT172,ARNT2,ARX,IDS,PEX14,GPSM2,CPT2,RBM12,RNPC3,KIF7,PTF1A,SNIP1</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2310</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Patient:34</t>
+          <t>Patient:482571</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -952,14 +1222,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SETD2,TKT,CBS,CRADD,GK,KCNH1,INPP5E,SOBP,GTF2E2,NAGLU</t>
-        </is>
+          <t>HFE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SETD2,TKT,CBS,CRADD,GK,KCNH1,INPP5E,SOBP,GTF2E2,NAGLU,SLC35A3,SRD5A3,ZDHHC9,PAK1,MAB21L1,HESX1,GPR88,MBTPS2,IFT172,ARNT2,ARX,IDS,PEX14,GPSM2,CPT2,RBM12,RNPC3,KIF7,PTF1A,SNIP1</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Patient:35</t>
+          <t>Patient:482572</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -969,14 +1247,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SETD2,TKT,CBS,CRADD,GK,KCNH1,INPP5E,SOBP,GTF2E2,NAGLU</t>
-        </is>
+          <t>NDUFB3</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SETD2,TKT,CBS,CRADD,GK,KCNH1,INPP5E,SOBP,GTF2E2,NAGLU,SLC35A3,SRD5A3,ZDHHC9,PAK1,MAB21L1,HESX1,GPR88,MBTPS2,IFT172,ARNT2,ARX,IDS,PEX14,GPSM2,CPT2,RBM12,RNPC3,KIF7,PTF1A,SNIP1</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>286</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Patient:36</t>
+          <t>Patient:482573</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -986,161 +1272,287 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SETD2,TKT,CBS,CRADD,GK,KCNH1,INPP5E,SOBP,GTF2E2,NAGLU</t>
-        </is>
+          <t>KIAA1109</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SETD2,TKT,CBS,CRADD,GK,KCNH1,INPP5E,SOBP,GTF2E2,NAGLU,SLC35A3,SRD5A3,ZDHHC9,PAK1,MAB21L1,HESX1,GPR88,MBTPS2,IFT172,ARNT2,ARX,IDS,PEX14,GPSM2,CPT2,RBM12,RNPC3,KIF7,PTF1A,SNIP1</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1849</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Patient:37</t>
+          <t>Patient:482574</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ciliary dyskinesia,Situs inversus totalis,Hearing impairment,Recurrent pneumonia,Sinusitis,Bronchiectasis</t>
+          <t>Autistic behavior,Intellectual disability,Seizures,Polycystic kidney dysplasia,Abnormal social behavior,Angiofibromas,Infantile spasms,Repetitive compulsive behavior,Abnormal social behavior,Delayed speech and language development,Polycystic kidney dysplasia</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IL2RA,GPNMB,PKHD1,CD3E,AK2,WDR72,MESP2,DLL3,MPL,DNAL4</t>
-        </is>
+          <t>SLC34A3</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SETD2,TKT,CBS,CRADD,GK,KCNH1,INPP5E,SOBP,GTF2E2,NAGLU,SLC35A3,SRD5A3,ZDHHC9,PAK1,MAB21L1,HESX1,GPR88,MBTPS2,IFT172,ARNT2,ARX,IDS,PEX14,GPSM2,CPT2,RBM12,RNPC3,KIF7,PTF1A,SNIP1</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1624</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Patient:38</t>
+          <t>Patient:482575</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Anxiety,High myopia,Muscular hypotonia,Clinodactyly,Neurological speech impairment,Intellectual disability,Global developmental delay,Prominent fingertip pads,Prominent nose,Muscular hypotonia,Abnormal facial shape</t>
+          <t>Ciliary dyskinesia,Situs inversus totalis,Hearing impairment,Recurrent pneumonia,Sinusitis,Bronchiectasis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TBCK,PIGS,DCPS,PPP2R5D,COG7,PAK3,TMEM237,TMEM107,SHROOM4,LAS1L</t>
-        </is>
+          <t>CCDC39</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>IL2RA,GPNMB,PKHD1,CD3E,AK2,WDR72,MESP2,DLL3,MPL,DNAL4,G6PC,DNAAF3,TARS1,CYP11B1,CDH23,ATP2B2,RSPH9,RPGR,LHX4,TBXAS1,INVS,ERCC8,NPHP4,GAS2L2,LEMD2,UROS,PEX1,DOCK2,FCGR3A,TDRD9</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>626</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Patient:39</t>
+          <t>Patient:482576</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Autistic behavior,Autism,Intellectual disability,Visual impairment</t>
+          <t>Anxiety,High myopia,Muscular hypotonia,Clinodactyly,Neurological speech impairment,Intellectual disability,Global developmental delay,Prominent fingertip pads,Prominent nose,Muscular hypotonia,Abnormal facial shape</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HIVEP2,FRA16E,GEMIN4,MECP2,EML1,ZSWIM6,CAMK2A,CPLX1,DAG1,PLK4</t>
-        </is>
+          <t>TCF4</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TBCK,PIGS,DCPS,PPP2R5D,COG7,PAK3,TMEM237,TMEM107,SHROOM4,LAS1L,ASH1L,PIGT,PEX1,OGT,HNRNPU,ARX,BCL11B,TAF1,CCND2,TUBB,FOXP1,UNC80,TRMT1,BCORL1,DDX3X,CASK,CLP1,CAMTA1,SLC45A1,EBF3</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>162</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Patient:41</t>
+          <t>Patient:482578</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Visual impairment,Bilateral conductive hearing impairment,Tinnitus,Myalgia,Muscle stiffness,Hypertonia,Distal lower limb amyotrophy,Arthralgia,Joint stiffness,Arthralgia,Single transverse palmar crease,Headache</t>
+          <t>Autistic behavior,Autism,Intellectual disability,Visual impairment</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SLC39A14,EPHB4,CA8,ERCC3,HADH,VCAN,ARHGDIA,AVPR2,ALDH3A2,CYB5R3</t>
-        </is>
+          <t>OCA2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HIVEP2,FRA16E,GEMIN4,MECP2,EML1,ZSWIM6,CAMK2A,CPLX1,DAG1,PLK4,AP1S2,EIF2S3,GRIN1,IQSEC2,AP4M1,ACY1,B4GAT1,CUL4B,NAT8L,RAB11B,PRUNE1,TUBA1A,PLAA,NDUFAF5,TBC1D23,UPB1,UBE3A,PCLO,TRIT1,MTHFS</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2707</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Patient:42</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Agenesis of corpus callosum</t>
-        </is>
-      </c>
+          <t>Patient:482579</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ARCN1,CDC42,ASXL1,HECW2,RPL10,OTUD6B,CDK10,WAC,KIAA1109,USP9X</t>
-        </is>
+          <t>COL1A1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>HIVEP2,FRA16E,GEMIN4,MECP2,EML1,ZSWIM6,CAMK2A,CPLX1,DAG1,PLK4,AP1S2,EIF2S3,GRIN1,IQSEC2,AP4M1,ACY1,B4GAT1,CUL4B,NAT8L,RAB11B,PRUNE1,TUBA1A,PLAA,NDUFAF5,TBC1D23,UPB1,UBE3A,PCLO,TRIT1,MTHFS</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2707</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Patient:43</t>
+          <t>Patient:482580</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Agenesis of corpus callosum</t>
+          <t>Visual impairment,Bilateral conductive hearing impairment,Tinnitus,Myalgia,Muscle stiffness,Hypertonia,Distal lower limb amyotrophy,Arthralgia,Joint stiffness,Arthralgia,Single transverse palmar crease,Headache</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ARCN1,CDC42,ASXL1,HECW2,RPL10,OTUD6B,CDK10,WAC,KIAA1109,USP9X</t>
-        </is>
+          <t>SGCA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SLC39A14,EPHB4,CA8,ERCC3,HADH,VCAN,ARHGDIA,AVPR2,ALDH3A2,CYB5R3,TSC1,TSC2,MTOR,GLUD1,NDUFB11,GFI1B,CLCNKA,CLCNKB,NF1,NARS2,PGM1,SCN11A,PRKAG2,DES,ZNF423,BMP15,CRYAB,NUP85,ALAS2,EFHC1</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4339</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Patient:44</t>
+          <t>Patient:482581</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Medulloblastoma,Encephalopathy,Severe global developmental delay,Motor delay,Delayed speech and language development,CNS hypomyelination,Abnormal myelination,Chorea,Athetosis,Progressive muscle weakness,Muscular hypotonia,Failure to thrive,Respiratory failure</t>
+          <t>Agenesis of corpus callosum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TUBA8,CNTNAP2,WDR45B,NDST1,NRXN1,GLRB,SUMF1,TPRKB,TMEM231,OSTM1</t>
-        </is>
+          <t>SOS1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ARCN1,CDC42,ASXL1,HECW2,RPL10,OTUD6B,CDK10,WAC,KIAA1109,USP9X,ATRX,RERE,HNRNPH2,KNL1,RAC1,PUS7,SLC9A7,SETD5,TCF20,HDAC8,HS6ST2,ASXL2,KIFBP,PQBP1,CCDC22,AUTS2,OSGEP,FBXO11,WDR4,ERCC5</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>635</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Patient:45</t>
+          <t>Patient:482582</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dandy-Walker malformation,Leukodystrophy</t>
+          <t>Agenesis of corpus callosum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>QARS1,FH,PARS2,CIT,AP4S1,AP4E1,YME1L1,ADK,EIF2S3,HCFC1</t>
-        </is>
+          <t>MPDZ</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ARCN1,CDC42,ASXL1,HECW2,RPL10,OTUD6B,CDK10,WAC,KIAA1109,USP9X,ATRX,RERE,HNRNPH2,KNL1,RAC1,PUS7,SLC9A7,SETD5,TCF20,HDAC8,HS6ST2,ASXL2,KIFBP,PQBP1,CCDC22,AUTS2,OSGEP,FBXO11,WDR4,ERCC5</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>528</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Patient:46</t>
+          <t>Patient:482583</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>Medulloblastoma,Encephalopathy,Severe global developmental delay,Motor delay,Delayed speech and language development,CNS hypomyelination,Abnormal myelination,Chorea,Athetosis,Progressive muscle weakness,Muscular hypotonia,Failure to thrive,Respiratory failure</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TUBB4A</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TUBA8,CNTNAP2,WDR45B,NDST1,NRXN1,GLRB,SUMF1,TPRKB,TMEM231,OSTM1,CACNA1B,SLC35A1,HSPD1,LAMB1,PNPO,DNM1,SLC25A1,COPB2,FKRP,PLEKHG2,ACADSB,RNASEH2A,TMEM107,DNM2,PPP3CA,SUOX,PEX12,WDR81,KCNB1,TRMT5</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Patient:482591</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Dandy-Walker malformation,Leukodystrophy</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>EIF2B4</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>QARS1,FH,PARS2,CIT,AP4S1,AP4E1,YME1L1,ADK,EIF2S3,HCFC1,DYRK1A,PGAP2,ZNHIT3,DHPS,GLE1,OCLN,SARS1,NAT8L,UQCC2,FKTN,EMC1,RAB11B,TOE1,RNF168,IER3IP1,POMT2,CCDC88C,AP3D1,DOCK7,PDHX</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Patient:482593</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>Autism,Global developmental delay,Motor delay,Delayed speech and language development,Muscular hypotonia,Obstructive sleep apnea,Dysphagia,Premature birth</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AP4M1,EIF2S3,RAB11B,AP1S2,TBC1D23,NAT8L,EML1,CPLX1,LAGE3,ZSWIM6</t>
-        </is>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>COL6A1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AP4M1,EIF2S3,RAB11B,AP1S2,TBC1D23,NAT8L,EML1,CPLX1,LAGE3,ZSWIM6,B4GAT1,GEMIN4,MECP2,AP4S1,AP4E1,FRA16E,PARS2,IQSEC2,TECPR2,UBE3A,IER3IP1,CLCN4,GRIN1,HIVEP2,ACER3,PRUNE1,UPB1,HSD17B4,CAMK2A,SARS1</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>670</v>
       </c>
     </row>
   </sheetData>
